--- a/data/processed/natural_assoc_trend.xlsx
+++ b/data/processed/natural_assoc_trend.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/yxu899_gatech_edu/Documents/Data/EM-DAT the Emergency Events Database/fig.natural_assoc_trend/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gtvault-my.sharepoint.com/personal/yxu899_gatech_edu/Documents/06_Research_PRJ_2025_Review/code/compound-hazard-review/data/processed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="8_{81170132-EB99-9A44-8156-EE7F5E518F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{389BC8B3-5215-4C4B-B389-5A0886EC6EEF}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="8_{81170132-EB99-9A44-8156-EE7F5E518F7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5361FD08-0E55-F844-A561-AC7F4D4631EF}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3ECCA74E-FB6D-6C4D-971B-5555482C59D1}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" xr2:uid="{3ECCA74E-FB6D-6C4D-971B-5555482C59D1}"/>
   </bookViews>
   <sheets>
     <sheet name="Damage" sheetId="4" r:id="rId1"/>
@@ -62,7 +62,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -576,9 +576,9 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -608,9 +608,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -646,9 +646,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -696,9 +696,9 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -728,9 +728,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -760,9 +760,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -802,9 +802,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -836,8 +836,8 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="2000">
-          <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
@@ -1119,9 +1119,9 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -1151,9 +1151,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1189,9 +1189,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1239,9 +1239,9 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -1271,9 +1271,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1303,9 +1303,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1346,9 +1346,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -1380,8 +1380,8 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="2000">
-          <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
@@ -1846,9 +1846,9 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -1878,9 +1878,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -1916,9 +1916,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -1966,9 +1966,9 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -1998,9 +1998,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -2030,9 +2030,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -2072,9 +2072,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -2106,8 +2106,8 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="2000">
-          <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
@@ -2389,9 +2389,9 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -2421,9 +2421,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -2459,9 +2459,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -2509,9 +2509,9 @@
                         <a:lumOff val="35000"/>
                       </a:schemeClr>
                     </a:solidFill>
-                    <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                    <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
@@ -2541,9 +2541,9 @@
                       <a:lumOff val="35000"/>
                     </a:schemeClr>
                   </a:solidFill>
-                  <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                  <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
               <a:endParaRPr lang="en-US"/>
@@ -2573,9 +2573,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="en-US"/>
@@ -2616,9 +2616,9 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="en-US"/>
@@ -2650,8 +2650,8 @@
     <a:p>
       <a:pPr>
         <a:defRPr sz="2000">
-          <a:latin typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
-          <a:cs typeface="helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:latin typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
+          <a:cs typeface="Helvetica" panose="020B0604020202020204" pitchFamily="34" charset="0"/>
         </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="en-US"/>
@@ -4931,16 +4931,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
+      <xdr:col>16</xdr:col>
       <xdr:colOff>224518</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>172808</xdr:rowOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>184678</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>524964</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>20626</xdr:rowOff>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>524965</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>32496</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5010,15 +5010,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>224518</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>605518</xdr:colOff>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>172808</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>673406</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>216206</xdr:colOff>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>117113</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -5365,15 +5365,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FF86036-FCAB-448C-BE27-213B5857CC0D}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5387,7 +5387,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>0.39513813906944845</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>0.36554753419595076</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
@@ -5432,7 +5432,7 @@
         <v>0.28429885484820377</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
@@ -5447,7 +5447,7 @@
         <v>0.63769287275677888</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
@@ -5462,7 +5462,7 @@
         <v>0.54894375420838304</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
@@ -5477,7 +5477,7 @@
         <v>0.88283762546710431</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
@@ -5492,7 +5492,7 @@
         <v>0.78730241628828901</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>0.51042021037496577</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>0.85237886286336373</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
@@ -5537,7 +5537,7 @@
         <v>0.61003316720237055</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
@@ -5552,7 +5552,7 @@
         <v>0.37658312424228557</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
@@ -5567,7 +5567,7 @@
         <v>0.25083682942512942</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
@@ -5582,7 +5582,7 @@
         <v>0.54858687805504214</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
@@ -5597,7 +5597,7 @@
         <v>0.4495083793952897</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
@@ -5612,7 +5612,7 @@
         <v>0.61995257627961953</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
@@ -5627,7 +5627,7 @@
         <v>0.39041919804730169</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>0.41183227502184466</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
@@ -5657,7 +5657,7 @@
         <v>0.84149118952622015</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
@@ -5672,7 +5672,7 @@
         <v>0.6145791378763158</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
@@ -5687,7 +5687,7 @@
         <v>0.66221781288169301</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
@@ -5702,7 +5702,7 @@
         <v>0.34107463446814107</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
@@ -5717,7 +5717,7 @@
         <v>0.66129013112628465</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
@@ -5732,7 +5732,7 @@
         <v>0.80433701953258308</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>0.593763062181348</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
@@ -5771,15 +5771,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6923CD-549A-9247-B48D-1CE8B736D85C}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
@@ -5808,7 +5808,7 @@
         <v>0.10199999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
@@ -5823,7 +5823,7 @@
         <v>6.7441860465116285E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
@@ -5838,7 +5838,7 @@
         <v>0.10860655737704918</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>0.31865284974093266</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>0.33078880407124683</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
@@ -5883,7 +5883,7 @@
         <v>0.33540372670807456</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
@@ -5898,7 +5898,7 @@
         <v>0.28758169934640521</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
@@ -5913,7 +5913,7 @@
         <v>0.34606741573033706</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
@@ -5928,7 +5928,7 @@
         <v>0.34190231362467866</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>0.27061855670103091</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
@@ -5958,7 +5958,7 @@
         <v>0.2361111111111111</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
@@ -5973,7 +5973,7 @@
         <v>0.25141242937853109</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>0.22102425876010781</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
@@ -6003,7 +6003,7 @@
         <v>0.23661971830985915</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>0.32748538011695905</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
@@ -6033,7 +6033,7 @@
         <v>0.30730478589420657</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
@@ -6048,7 +6048,7 @@
         <v>0.31232091690544411</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
@@ -6063,7 +6063,7 @@
         <v>0.39083557951482478</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
@@ -6078,7 +6078,7 @@
         <v>0.32238805970149254</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
@@ -6093,7 +6093,7 @@
         <v>0.27522935779816515</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
@@ -6108,7 +6108,7 @@
         <v>0.32116788321167883</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
@@ -6123,7 +6123,7 @@
         <v>0.38356164383561642</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>0.33027522935779818</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
@@ -6153,7 +6153,7 @@
         <v>0.34565217391304348</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
@@ -6177,15 +6177,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71CCB196-8DDD-4F58-BF1F-F73C8BA65DE7}">
   <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultRowHeight="15.75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6199,7 +6199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>2000</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>9.2224231464737794E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2001</v>
       </c>
@@ -6229,7 +6229,7 @@
         <v>8.7567540143578301E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>2002</v>
       </c>
@@ -6244,7 +6244,7 @@
         <v>0.18376334306639222</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>2003</v>
       </c>
@@ -6259,7 +6259,7 @@
         <v>0.64185873803145643</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>2004</v>
       </c>
@@ -6274,7 +6274,7 @@
         <v>3.7065037494125583E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>2005</v>
       </c>
@@ -6289,7 +6289,7 @@
         <v>9.0026204609872179E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>2006</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v>0.2617955329337307</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>2007</v>
       </c>
@@ -6319,7 +6319,7 @@
         <v>0.50618496851694728</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>2008</v>
       </c>
@@ -6334,7 +6334,7 @@
         <v>0.96073026905736947</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>2009</v>
       </c>
@@ -6349,7 +6349,7 @@
         <v>0.36192494701408801</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>2010</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v>1.5010585552159967E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>2011</v>
       </c>
@@ -6379,7 +6379,7 @@
         <v>0.17653264564529364</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>2012</v>
       </c>
@@ -6394,7 +6394,7 @@
         <v>0.18098106712564543</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>2013</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>0.68928105163642917</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>2014</v>
       </c>
@@ -6424,7 +6424,7 @@
         <v>0.20745954227712343</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>2015</v>
       </c>
@@ -6439,7 +6439,7 @@
         <v>0.47813578826237052</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>2016</v>
       </c>
@@ -6454,7 +6454,7 @@
         <v>0.28024231127679405</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>2017</v>
       </c>
@@ -6469,7 +6469,7 @@
         <v>0.45508730691739424</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>2018</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>0.20382763149665395</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>2019</v>
       </c>
@@ -6499,7 +6499,7 @@
         <v>0.23888300688194813</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>2020</v>
       </c>
@@ -6514,7 +6514,7 @@
         <v>0.34849638370765129</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>2021</v>
       </c>
@@ -6529,7 +6529,7 @@
         <v>0.31671112935221285</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>2022</v>
       </c>
@@ -6544,7 +6544,7 @@
         <v>9.6194923252694853E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>2023</v>
       </c>
@@ -6559,7 +6559,7 @@
         <v>0.16628333213541294</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>2024</v>
       </c>
